--- a/data/CS7/Market Data/CS7_market_data_2030.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2030.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AB8659-E4E0-47C2-BD99-4C5DA2F11D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCD122C-5F06-4F74-A12F-5E3118130E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-12555" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>

--- a/data/CS7/Market Data/CS7_market_data_2030.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2030.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCD122C-5F06-4F74-A12F-5E3118130E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2811C86-9419-4D3E-B308-5587D1876515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2030.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2030.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2811C86-9419-4D3E-B308-5587D1876515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0A897-B3AE-4EAD-BEB0-14CE7017DB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35115" yWindow="-9900" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2030.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2030.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0A897-B3AE-4EAD-BEB0-14CE7017DB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B139412-9E3C-4D71-AE75-FF9474300CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35115" yWindow="-9900" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31485" yWindow="-11700" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2030.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2030.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B139412-9E3C-4D71-AE75-FF9474300CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6EDD81-454A-49E1-B363-6D06F08566CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31485" yWindow="-11700" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32790" yWindow="-10395" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -2237,19 +2237,19 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
         <f>1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" ref="D1:E1" si="0">1/$B$1</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>

--- a/data/CS7/Market Data/CS7_market_data_2030.xlsx
+++ b/data/CS7/Market Data/CS7_market_data_2030.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6EDD81-454A-49E1-B363-6D06F08566CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409ABE17-F4FA-44BE-8346-071185BEFB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32790" yWindow="-10395" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32355" yWindow="-10830" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
